--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="195">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -595,6 +595,15 @@
   </si>
   <si>
     <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/24</t>
+  </si>
+  <si>
+    <t>1405/06/25</t>
+  </si>
+  <si>
+    <t>سیگار</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1150,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3209,27 +3218,37 @@
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
-      </c>
-      <c r="B148" s="8"/>
+        <v>3302600</v>
+      </c>
+      <c r="B148" s="8">
+        <v>112000</v>
+      </c>
       <c r="C148" s="8"/>
       <c r="D148" s="1"/>
-      <c r="E148" s="1"/>
+      <c r="E148" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
-      </c>
-      <c r="B149" s="8"/>
+        <v>3452600</v>
+      </c>
+      <c r="B149" s="8">
+        <v>150000</v>
+      </c>
       <c r="C149" s="8"/>
-      <c r="D149" s="1"/>
-      <c r="E149" s="1"/>
+      <c r="D149" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -3239,7 +3258,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -3249,7 +3268,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -3259,7 +3278,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3269,7 +3288,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3279,7 +3298,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3289,7 +3308,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3299,7 +3318,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3309,7 +3328,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3319,7 +3338,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3329,7 +3348,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3339,7 +3358,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3349,7 +3368,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3359,7 +3378,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3369,7 +3388,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3380,7 +3399,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15091600</v>
+        <v>15353600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3391,7 +3410,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="197">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -604,6 +604,12 @@
   </si>
   <si>
     <t>سیگار</t>
+  </si>
+  <si>
+    <t>1405/06/27</t>
+  </si>
+  <si>
+    <t>وجه عرق</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1156,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3248,17 +3254,23 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="1"/>
-      <c r="E150" s="1"/>
+      <c r="C150" s="8">
+        <v>500000</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -3268,7 +3280,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -3278,7 +3290,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3288,7 +3300,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3298,7 +3310,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3308,7 +3320,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3318,7 +3330,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3328,7 +3340,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3338,7 +3350,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3348,7 +3360,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3358,7 +3370,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3368,7 +3380,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3378,7 +3390,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3388,7 +3400,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3403,14 +3415,14 @@
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
-        <v>11901000</v>
+        <v>12401000</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="197">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3270,17 +3270,21 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
-      </c>
-      <c r="B151" s="8"/>
+        <v>3102600</v>
+      </c>
+      <c r="B151" s="8">
+        <v>150000</v>
+      </c>
       <c r="C151" s="8"/>
-      <c r="D151" s="1"/>
+      <c r="D151" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="E151" s="1"/>
     </row>
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -3290,7 +3294,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3300,7 +3304,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3310,7 +3314,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3320,7 +3324,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3330,7 +3334,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3340,7 +3344,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3350,7 +3354,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3360,7 +3364,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3370,7 +3374,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3380,7 +3384,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3390,7 +3394,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3400,7 +3404,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3411,7 +3415,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15353600</v>
+        <v>15503600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3422,7 +3426,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="199">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -610,6 +610,12 @@
   </si>
   <si>
     <t>وجه عرق</t>
+  </si>
+  <si>
+    <t>1405/07/02</t>
+  </si>
+  <si>
+    <t>بستنی کیک</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1162,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3284,17 +3290,23 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
-      </c>
-      <c r="B152" s="8"/>
+        <v>3282600</v>
+      </c>
+      <c r="B152" s="8">
+        <v>180000</v>
+      </c>
       <c r="C152" s="8"/>
-      <c r="D152" s="1"/>
-      <c r="E152" s="1"/>
+      <c r="D152" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3304,7 +3316,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3314,7 +3326,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3324,7 +3336,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3334,7 +3346,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3344,7 +3356,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3354,7 +3366,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3364,7 +3376,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3374,7 +3386,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3384,7 +3396,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3394,7 +3406,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3404,7 +3416,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3415,7 +3427,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15503600</v>
+        <v>15683600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3426,7 +3438,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="201">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -616,6 +616,12 @@
   </si>
   <si>
     <t>بستنی کیک</t>
+  </si>
+  <si>
+    <t>1405/07/23</t>
+  </si>
+  <si>
+    <t>دنگ مزه پل ذوآب</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1168,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3306,17 +3312,23 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
-      </c>
-      <c r="B153" s="8"/>
+        <v>3471600</v>
+      </c>
+      <c r="B153" s="8">
+        <v>189000</v>
+      </c>
       <c r="C153" s="8"/>
-      <c r="D153" s="1"/>
-      <c r="E153" s="1"/>
+      <c r="D153" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3326,7 +3338,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3336,7 +3348,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3346,7 +3358,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3356,7 +3368,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3366,7 +3378,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3376,7 +3388,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3386,7 +3398,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3396,7 +3408,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3406,7 +3418,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3416,7 +3428,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3427,7 +3439,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15683600</v>
+        <v>15872600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3438,7 +3450,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="199">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -616,12 +616,6 @@
   </si>
   <si>
     <t>بستنی کیک</t>
-  </si>
-  <si>
-    <t>1405/07/23</t>
-  </si>
-  <si>
-    <t>دنگ مزه پل ذوآب</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1162,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3312,23 +3306,17 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
-      </c>
-      <c r="B153" s="8">
-        <v>189000</v>
-      </c>
+        <v>3282600</v>
+      </c>
+      <c r="B153" s="8"/>
       <c r="C153" s="8"/>
-      <c r="D153" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>199</v>
-      </c>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
     </row>
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3338,7 +3326,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3348,7 +3336,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3358,7 +3346,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3368,7 +3356,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3378,7 +3366,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3388,7 +3376,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3398,7 +3386,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3408,7 +3396,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3418,7 +3406,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3428,7 +3416,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3439,7 +3427,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15872600</v>
+        <v>15683600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3450,7 +3438,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="201">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -616,6 +616,12 @@
   </si>
   <si>
     <t>بستنی کیک</t>
+  </si>
+  <si>
+    <t>1405/07/23</t>
+  </si>
+  <si>
+    <t>بستنی</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1168,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3306,17 +3312,23 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
-      </c>
-      <c r="B153" s="8"/>
+        <v>3342600</v>
+      </c>
+      <c r="B153" s="8">
+        <v>60000</v>
+      </c>
       <c r="C153" s="8"/>
-      <c r="D153" s="1"/>
-      <c r="E153" s="1"/>
+      <c r="D153" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3326,7 +3338,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3336,7 +3348,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3346,7 +3358,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3356,7 +3368,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3366,7 +3378,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3376,7 +3388,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3386,7 +3398,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3396,7 +3408,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3406,7 +3418,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3416,7 +3428,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3427,7 +3439,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15683600</v>
+        <v>15743600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3438,7 +3450,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="202">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -622,6 +622,9 @@
   </si>
   <si>
     <t>بستنی</t>
+  </si>
+  <si>
+    <t>1405/07/28</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1171,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3328,17 +3331,23 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
-      </c>
-      <c r="B154" s="8"/>
+        <v>3492600</v>
+      </c>
+      <c r="B154" s="8">
+        <v>150000</v>
+      </c>
       <c r="C154" s="8"/>
-      <c r="D154" s="1"/>
-      <c r="E154" s="1"/>
+      <c r="D154" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3348,7 +3357,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3358,7 +3367,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3368,7 +3377,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3378,7 +3387,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3388,7 +3397,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3398,7 +3407,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3408,7 +3417,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3418,7 +3427,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3428,7 +3437,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3439,7 +3448,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15743600</v>
+        <v>15893600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3450,7 +3459,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="203">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -625,6 +625,9 @@
   </si>
   <si>
     <t>1405/07/28</t>
+  </si>
+  <si>
+    <t>1405/08/07</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1174,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3347,17 +3350,23 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B155" s="8"/>
-      <c r="C155" s="8"/>
-      <c r="D155" s="1"/>
-      <c r="E155" s="1"/>
+      <c r="C155" s="8">
+        <v>2000000</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3367,7 +3376,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3377,7 +3386,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3387,7 +3396,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3397,7 +3406,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3407,7 +3416,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3417,7 +3426,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3427,7 +3436,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3437,7 +3446,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3452,14 +3461,14 @@
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
-        <v>12401000</v>
+        <v>14401000</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="204">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -628,6 +628,9 @@
   </si>
   <si>
     <t>1405/08/07</t>
+  </si>
+  <si>
+    <t>1405/08/08</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1177,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3366,17 +3369,23 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
-      </c>
-      <c r="B156" s="8"/>
+        <v>1672600</v>
+      </c>
+      <c r="B156" s="8">
+        <v>180000</v>
+      </c>
       <c r="C156" s="8"/>
-      <c r="D156" s="1"/>
-      <c r="E156" s="1"/>
+      <c r="D156" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3386,7 +3395,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3396,7 +3405,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3406,7 +3415,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3416,7 +3425,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3426,7 +3435,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3436,7 +3445,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3446,7 +3455,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3457,7 +3466,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15893600</v>
+        <v>16073600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3468,7 +3477,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="205">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -631,6 +631,9 @@
   </si>
   <si>
     <t>1405/08/08</t>
+  </si>
+  <si>
+    <t>پفک نوشابه</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1180,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3385,17 +3388,23 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>1672600</v>
-      </c>
-      <c r="B157" s="8"/>
+        <v>1872600</v>
+      </c>
+      <c r="B157" s="8">
+        <v>200000</v>
+      </c>
       <c r="C157" s="8"/>
-      <c r="D157" s="1"/>
-      <c r="E157" s="1"/>
+      <c r="D157" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3405,7 +3414,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3415,7 +3424,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3425,7 +3434,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3435,7 +3444,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3445,7 +3454,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3455,7 +3464,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3466,7 +3475,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>16073600</v>
+        <v>16273600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3477,7 +3486,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>
